--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diasr\OneDrive\Área de Trabalho\Docs Para Salvar\FLYUP EMPREENDIMENTOS\REPORT FINANCEIRO\CLAUDE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diasr\OneDrive\Área de Trabalho\Docs Para Salvar\FLYUP EMPREENDIMENTOS\REPORT FINANCEIRO\CLAUDE\Dashboard Financeiro Gerencial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1631AD-2842-42D5-BA73-01E222621C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F7B919-ACFA-4EC2-B9F4-492992606672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2061AD2-1719-4795-BDD0-49664C0E8E6C}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F2061AD2-1719-4795-BDD0-49664C0E8E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Apresentação de Resultados" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="485">
   <si>
     <t>Período</t>
   </si>
@@ -1423,6 +1423,75 @@
   </si>
   <si>
     <t>Assinatura de Mapas</t>
+  </si>
+  <si>
+    <t>93.319,96</t>
+  </si>
+  <si>
+    <t>93.312,76</t>
+  </si>
+  <si>
+    <t>10.142,69</t>
+  </si>
+  <si>
+    <t>2.187,46</t>
+  </si>
+  <si>
+    <t>49.653,34</t>
+  </si>
+  <si>
+    <t>3.097,72</t>
+  </si>
+  <si>
+    <t>-156.892,23</t>
+  </si>
+  <si>
+    <t>-24.237,69</t>
+  </si>
+  <si>
+    <t>-21.349,93</t>
+  </si>
+  <si>
+    <t>-2.031,43</t>
+  </si>
+  <si>
+    <t>-18.918,50</t>
+  </si>
+  <si>
+    <t>-132.654,54</t>
+  </si>
+  <si>
+    <t>-128.369,96</t>
+  </si>
+  <si>
+    <t>-3.587,52</t>
+  </si>
+  <si>
+    <t>-21.360,89</t>
+  </si>
+  <si>
+    <t>-2.355,27</t>
+  </si>
+  <si>
+    <t>-67.500,00</t>
+  </si>
+  <si>
+    <t>-1.875,46</t>
+  </si>
+  <si>
+    <t>-29.053,84</t>
+  </si>
+  <si>
+    <t>-2.636,98</t>
+  </si>
+  <si>
+    <t>-4.284,58</t>
+  </si>
+  <si>
+    <t>-63.572,27</t>
+  </si>
+  <si>
+    <t>212.479,95</t>
   </si>
 </sst>
 </file>
@@ -1537,7 +1606,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1641,21 +1710,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </left>
@@ -1704,14 +1758,42 @@
       <left style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
       <bottom style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1720,7 +1802,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1733,59 +1815,62 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="43" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="17" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="8" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1796,17 +1881,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2100,23 +2175,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13CF3071-88CD-4317-BBD4-A331D4E0BCB3}" name="Tabela1" displayName="Tabela1" ref="A1:N82" totalsRowShown="0">
-  <autoFilter ref="A1:N82" xr:uid="{13CF3071-88CD-4317-BBD4-A331D4E0BCB3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13CF3071-88CD-4317-BBD4-A331D4E0BCB3}" name="Tabela1" displayName="Tabela1" ref="A1:N87" totalsRowShown="0">
+  <autoFilter ref="A1:N87" xr:uid="{13CF3071-88CD-4317-BBD4-A331D4E0BCB3}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{6C3F0641-073B-4AB8-AC47-D6B967EE32D6}" name="Período" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{6BBB7394-1647-44F4-B5FD-9E7F70645951}" name="Receitas Fixas" dataDxfId="21" dataCellStyle="Vírgula"/>
-    <tableColumn id="3" xr3:uid="{6351567B-AAD5-458D-83C4-296882B7B4EA}" name="Receitas Variáveis" dataDxfId="20" dataCellStyle="Vírgula"/>
-    <tableColumn id="4" xr3:uid="{0AC531E6-5F3F-4597-B8D3-1286AD659A89}" name="Despesas Fixas" dataDxfId="19" dataCellStyle="Vírgula"/>
-    <tableColumn id="5" xr3:uid="{1A94668B-6B5C-459C-915F-05028B9FC5F6}" name="Despesas Variáveis" dataDxfId="18" dataCellStyle="Vírgula"/>
-    <tableColumn id="6" xr3:uid="{D156C819-05AF-4A60-AA11-58A00A251F57}" name="Receitas Consolidadas" dataDxfId="17" dataCellStyle="Vírgula"/>
-    <tableColumn id="7" xr3:uid="{0BDF83EF-7D4D-49A4-AA1A-973485B969E7}" name="Despesas Consolidadas" dataDxfId="16" dataCellStyle="Vírgula"/>
-    <tableColumn id="8" xr3:uid="{DDA26083-ACD4-4813-9182-6F238A06A730}" name="Geração do Caixa do Período" dataDxfId="15" dataCellStyle="Vírgula"/>
-    <tableColumn id="9" xr3:uid="{494F7EA7-8202-4671-9A9C-F96B17DBC7A0}" name="Saldo Conta Corrente" dataDxfId="14" dataCellStyle="Vírgula"/>
-    <tableColumn id="10" xr3:uid="{5957A9FD-1181-4478-A50B-9D182C596B7A}" name="Saldo Contas de Aplicação" dataDxfId="13" dataCellStyle="Vírgula"/>
-    <tableColumn id="11" xr3:uid="{5ABDA88B-D373-4DA8-AE9C-D8962ECBFEF6}" name="Saldo Total Das Contas" dataDxfId="12" dataCellStyle="Vírgula"/>
-    <tableColumn id="12" xr3:uid="{3D04213A-CEE1-4BF0-9F52-1EB9C03180E2}" name="Total de Horas" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{6C3F0641-073B-4AB8-AC47-D6B967EE32D6}" name="Período" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{6BBB7394-1647-44F4-B5FD-9E7F70645951}" name="Receitas Fixas" dataDxfId="20" dataCellStyle="Vírgula"/>
+    <tableColumn id="3" xr3:uid="{6351567B-AAD5-458D-83C4-296882B7B4EA}" name="Receitas Variáveis" dataDxfId="19" dataCellStyle="Vírgula"/>
+    <tableColumn id="4" xr3:uid="{0AC531E6-5F3F-4597-B8D3-1286AD659A89}" name="Despesas Fixas" dataDxfId="18" dataCellStyle="Vírgula"/>
+    <tableColumn id="5" xr3:uid="{1A94668B-6B5C-459C-915F-05028B9FC5F6}" name="Despesas Variáveis" dataDxfId="17" dataCellStyle="Vírgula"/>
+    <tableColumn id="6" xr3:uid="{D156C819-05AF-4A60-AA11-58A00A251F57}" name="Receitas Consolidadas" dataDxfId="16" dataCellStyle="Vírgula"/>
+    <tableColumn id="7" xr3:uid="{0BDF83EF-7D4D-49A4-AA1A-973485B969E7}" name="Despesas Consolidadas" dataDxfId="15" dataCellStyle="Vírgula"/>
+    <tableColumn id="8" xr3:uid="{DDA26083-ACD4-4813-9182-6F238A06A730}" name="Geração do Caixa do Período" dataDxfId="14" dataCellStyle="Vírgula"/>
+    <tableColumn id="9" xr3:uid="{494F7EA7-8202-4671-9A9C-F96B17DBC7A0}" name="Saldo Conta Corrente" dataDxfId="13" dataCellStyle="Vírgula"/>
+    <tableColumn id="10" xr3:uid="{5957A9FD-1181-4478-A50B-9D182C596B7A}" name="Saldo Contas de Aplicação" dataDxfId="12" dataCellStyle="Vírgula"/>
+    <tableColumn id="11" xr3:uid="{5ABDA88B-D373-4DA8-AE9C-D8962ECBFEF6}" name="Saldo Total Das Contas" dataDxfId="11" dataCellStyle="Vírgula"/>
+    <tableColumn id="12" xr3:uid="{3D04213A-CEE1-4BF0-9F52-1EB9C03180E2}" name="Total de Horas" dataDxfId="10"/>
     <tableColumn id="13" xr3:uid="{391341A1-5CF6-46BD-A3BD-586A1AED7EC0}" name="Socios"/>
-    <tableColumn id="14" xr3:uid="{254408E5-D1C5-430A-B649-F614EAE85C70}" name="Horas de Voos" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{254408E5-D1C5-430A-B649-F614EAE85C70}" name="Horas de Voos" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2439,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8CD55EC-DA9F-4C69-946B-5012EDBA0186}">
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -6093,6 +6168,256 @@
         <v>0.12013888888888889</v>
       </c>
     </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B83" s="2">
+        <v>28000</v>
+      </c>
+      <c r="C83" s="2">
+        <f>93319.96-Tabela1[[#This Row],[Receitas Fixas]]</f>
+        <v>65319.960000000006</v>
+      </c>
+      <c r="D83" s="2">
+        <f>18918.5+2031.43+1943.18+400</f>
+        <v>23293.11</v>
+      </c>
+      <c r="E83" s="2">
+        <f>156892.23-Tabela1[[#This Row],[Despesas Fixas]]</f>
+        <v>133599.12</v>
+      </c>
+      <c r="F83" s="2">
+        <f>Tabela1[[#This Row],[Receitas Fixas]]+Tabela1[[#This Row],[Receitas Variáveis]]</f>
+        <v>93319.96</v>
+      </c>
+      <c r="G83" s="2">
+        <f>Tabela1[[#This Row],[Despesas Fixas]]+Tabela1[[#This Row],[Despesas Variáveis]]</f>
+        <v>156892.22999999998</v>
+      </c>
+      <c r="H83" s="2">
+        <v>-63572.27</v>
+      </c>
+      <c r="I83" s="2">
+        <v>19168.650000000001</v>
+      </c>
+      <c r="J83" s="2">
+        <v>193311.3</v>
+      </c>
+      <c r="K83" s="2">
+        <f>Tabela1[[#This Row],[Saldo Conta Corrente]]+Tabela1[[#This Row],[Saldo Contas de Aplicação]]</f>
+        <v>212479.94999999998</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0.93263888888888891</v>
+      </c>
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0.28333333333333333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B84" s="2">
+        <v>28000</v>
+      </c>
+      <c r="C84" s="2">
+        <f>93319.96-Tabela1[[#This Row],[Receitas Fixas]]</f>
+        <v>65319.960000000006</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" ref="D84:D87" si="1">18918.5+2031.43+1943.18+400</f>
+        <v>23293.11</v>
+      </c>
+      <c r="E84" s="2">
+        <f>156892.23-Tabela1[[#This Row],[Despesas Fixas]]</f>
+        <v>133599.12</v>
+      </c>
+      <c r="F84" s="2">
+        <f>Tabela1[[#This Row],[Receitas Fixas]]+Tabela1[[#This Row],[Receitas Variáveis]]</f>
+        <v>93319.96</v>
+      </c>
+      <c r="G84" s="2">
+        <f>Tabela1[[#This Row],[Despesas Fixas]]+Tabela1[[#This Row],[Despesas Variáveis]]</f>
+        <v>156892.22999999998</v>
+      </c>
+      <c r="H84" s="2">
+        <v>-63572.27</v>
+      </c>
+      <c r="I84" s="2">
+        <v>19168.650000000001</v>
+      </c>
+      <c r="J84" s="2">
+        <v>193311.3</v>
+      </c>
+      <c r="K84" s="2">
+        <f>Tabela1[[#This Row],[Saldo Conta Corrente]]+Tabela1[[#This Row],[Saldo Contas de Aplicação]]</f>
+        <v>212479.94999999998</v>
+      </c>
+      <c r="L84" s="3">
+        <v>0.93263888888888891</v>
+      </c>
+      <c r="M84" t="s">
+        <v>16</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0.16944444444444445</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B85" s="2">
+        <v>28000</v>
+      </c>
+      <c r="C85" s="2">
+        <f>93319.96-Tabela1[[#This Row],[Receitas Fixas]]</f>
+        <v>65319.960000000006</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="1"/>
+        <v>23293.11</v>
+      </c>
+      <c r="E85" s="2">
+        <f>156892.23-Tabela1[[#This Row],[Despesas Fixas]]</f>
+        <v>133599.12</v>
+      </c>
+      <c r="F85" s="2">
+        <f>Tabela1[[#This Row],[Receitas Fixas]]+Tabela1[[#This Row],[Receitas Variáveis]]</f>
+        <v>93319.96</v>
+      </c>
+      <c r="G85" s="2">
+        <f>Tabela1[[#This Row],[Despesas Fixas]]+Tabela1[[#This Row],[Despesas Variáveis]]</f>
+        <v>156892.22999999998</v>
+      </c>
+      <c r="H85" s="2">
+        <v>-63572.27</v>
+      </c>
+      <c r="I85" s="2">
+        <v>19168.650000000001</v>
+      </c>
+      <c r="J85" s="2">
+        <v>193311.3</v>
+      </c>
+      <c r="K85" s="2">
+        <f>Tabela1[[#This Row],[Saldo Conta Corrente]]+Tabela1[[#This Row],[Saldo Contas de Aplicação]]</f>
+        <v>212479.94999999998</v>
+      </c>
+      <c r="L85" s="3">
+        <v>0.93263888888888891</v>
+      </c>
+      <c r="M85" t="s">
+        <v>24</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0.37430555555555556</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B86" s="2">
+        <v>28000</v>
+      </c>
+      <c r="C86" s="2">
+        <f>93319.96-Tabela1[[#This Row],[Receitas Fixas]]</f>
+        <v>65319.960000000006</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="1"/>
+        <v>23293.11</v>
+      </c>
+      <c r="E86" s="2">
+        <f>156892.23-Tabela1[[#This Row],[Despesas Fixas]]</f>
+        <v>133599.12</v>
+      </c>
+      <c r="F86" s="2">
+        <f>Tabela1[[#This Row],[Receitas Fixas]]+Tabela1[[#This Row],[Receitas Variáveis]]</f>
+        <v>93319.96</v>
+      </c>
+      <c r="G86" s="2">
+        <f>Tabela1[[#This Row],[Despesas Fixas]]+Tabela1[[#This Row],[Despesas Variáveis]]</f>
+        <v>156892.22999999998</v>
+      </c>
+      <c r="H86" s="2">
+        <v>-63572.27</v>
+      </c>
+      <c r="I86" s="2">
+        <v>19168.650000000001</v>
+      </c>
+      <c r="J86" s="2">
+        <v>193311.3</v>
+      </c>
+      <c r="K86" s="2">
+        <f>Tabela1[[#This Row],[Saldo Conta Corrente]]+Tabela1[[#This Row],[Saldo Contas de Aplicação]]</f>
+        <v>212479.94999999998</v>
+      </c>
+      <c r="L86" s="3">
+        <v>0.93263888888888891</v>
+      </c>
+      <c r="M86" t="s">
+        <v>15</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0.10555555555555556</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B87" s="2">
+        <v>28000</v>
+      </c>
+      <c r="C87" s="2">
+        <f>93319.96-Tabela1[[#This Row],[Receitas Fixas]]</f>
+        <v>65319.960000000006</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="1"/>
+        <v>23293.11</v>
+      </c>
+      <c r="E87" s="2">
+        <f>156892.23-Tabela1[[#This Row],[Despesas Fixas]]</f>
+        <v>133599.12</v>
+      </c>
+      <c r="F87" s="2">
+        <f>Tabela1[[#This Row],[Receitas Fixas]]+Tabela1[[#This Row],[Receitas Variáveis]]</f>
+        <v>93319.96</v>
+      </c>
+      <c r="G87" s="2">
+        <f>Tabela1[[#This Row],[Despesas Fixas]]+Tabela1[[#This Row],[Despesas Variáveis]]</f>
+        <v>156892.22999999998</v>
+      </c>
+      <c r="H87" s="2">
+        <v>-63572.27</v>
+      </c>
+      <c r="I87" s="2">
+        <v>19168.650000000001</v>
+      </c>
+      <c r="J87" s="2">
+        <v>193311.3</v>
+      </c>
+      <c r="K87" s="2">
+        <f>Tabela1[[#This Row],[Saldo Conta Corrente]]+Tabela1[[#This Row],[Saldo Contas de Aplicação]]</f>
+        <v>212479.94999999998</v>
+      </c>
+      <c r="L87" s="3">
+        <v>0.93263888888888891</v>
+      </c>
+      <c r="M87" t="s">
+        <v>14</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0.12847222222222221</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
@@ -6103,14 +6428,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2C35A7-AD09-4FE0-ACFD-C89086CACEA9}">
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
-    <col min="2" max="19" width="15.7109375" customWidth="1"/>
+    <col min="2" max="20" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>25</v>
       </c>
@@ -6134,8 +6459,9 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="32"/>
       <c r="S1" s="33"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T1" s="34"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
@@ -6190,2963 +6516,3087 @@
       <c r="R2" s="4">
         <v>46143</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="4">
         <v>46174</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="T2" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="9" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="T3" s="24" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="S4" s="14" t="s">
+      <c r="S4" s="11" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="T4" s="25" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="P5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="Q5" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="R5" s="16" t="s">
+      <c r="R5" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="S5" s="17" t="s">
+      <c r="S5" s="13" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="T5" s="26" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="13">
         <v>424.74</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="L6" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="M6" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="O6" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="P6" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="Q6" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="R6" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="S6" s="17" t="s">
+      <c r="S6" s="13" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="T6" s="26" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="16">
-        <v>0</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="D7" s="13">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="16">
-        <v>0</v>
-      </c>
-      <c r="H7" s="16" t="s">
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="13">
         <v>902.17</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="13">
         <v>878.39</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="13">
         <v>878.39</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="13">
         <v>662.44</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="O7" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="P7" s="16" t="s">
+      <c r="P7" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="Q7" s="16" t="s">
+      <c r="Q7" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="R7" s="16" t="s">
+      <c r="R7" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="17" t="s">
+      <c r="S7" s="13" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="T7" s="26" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16">
-        <v>0</v>
-      </c>
-      <c r="C8" s="16">
-        <v>0</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0</v>
-      </c>
-      <c r="E8" s="16">
-        <v>0</v>
-      </c>
-      <c r="F8" s="16">
-        <v>0</v>
-      </c>
-      <c r="G8" s="16">
-        <v>0</v>
-      </c>
-      <c r="H8" s="16">
-        <v>0</v>
-      </c>
-      <c r="I8" s="16">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16">
+      <c r="B8" s="13">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
         <v>700</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="13">
         <v>700</v>
       </c>
-      <c r="M8" s="16">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="19"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="27"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L9" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="O9" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="P9" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="Q9" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="R9" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="S9" s="17" t="s">
+      <c r="S9" s="13" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="T9" s="26" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13">
         <v>679.6</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="13">
         <v>892.2</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="O10" s="16" t="s">
+      <c r="O10" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="P10" s="16" t="s">
+      <c r="P10" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="Q10" s="16" t="s">
+      <c r="Q10" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="R10" s="16" t="s">
+      <c r="R10" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="S10" s="17" t="s">
+      <c r="S10" s="13" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="T10" s="26" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="O11" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="P11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="Q11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="R11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="S11" s="17" t="s">
+      <c r="S11" s="13" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="T11" s="26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="13">
         <v>826.46</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="13">
         <v>553.86</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="13">
         <v>895.35</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="13">
         <v>824.44</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="13">
         <v>723.2</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="13">
         <v>299.82</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="13">
         <v>938.92</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="13">
         <v>499.06</v>
       </c>
-      <c r="O12" s="16">
+      <c r="O12" s="13">
         <v>421.55</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="13">
         <v>498.88</v>
       </c>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="16">
+      <c r="Q12" s="14"/>
+      <c r="R12" s="13">
         <v>143.83000000000001</v>
       </c>
-      <c r="S12" s="17" t="s">
+      <c r="S12" s="13" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="T12" s="26">
+        <v>231.55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>6</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="11">
         <v>4.8</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="11">
         <v>5.7</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="11">
         <v>6</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="11">
         <v>6.6</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="11">
         <v>6.3</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="11">
         <v>9.3000000000000007</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="11">
         <v>8.1</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="11">
         <v>6.3</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="11">
         <v>5.4</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="11">
         <v>4.2</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="11">
         <v>5.4</v>
       </c>
-      <c r="O13" s="13">
+      <c r="O13" s="11">
         <v>5.7</v>
       </c>
-      <c r="P13" s="13">
+      <c r="P13" s="11">
         <v>6.9</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="Q13" s="11">
         <v>4.2</v>
       </c>
-      <c r="R13" s="13">
+      <c r="R13" s="11">
         <v>6.6</v>
       </c>
-      <c r="S13" s="14">
+      <c r="S13" s="11">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="T13" s="25">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="13">
         <v>6</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="13">
         <v>4.8</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="13">
         <v>5.7</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="13">
         <v>6</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="13">
         <v>6.6</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="13">
         <v>5.0999999999999996</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="13">
         <v>6.3</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="13">
         <v>9.3000000000000007</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="13">
         <v>8.1</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="13">
         <v>6.3</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="13">
         <v>5.4</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="13">
         <v>4.2</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="13">
         <v>5.4</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O14" s="13">
         <v>5.7</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="13">
         <v>6.9</v>
       </c>
-      <c r="Q14" s="20">
+      <c r="Q14" s="15">
         <v>4.2</v>
       </c>
-      <c r="R14" s="20">
+      <c r="R14" s="15">
         <v>6.6</v>
       </c>
-      <c r="S14" s="21">
+      <c r="S14" s="15">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="T14" s="28">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="13">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="s">
+      <c r="B15" s="11">
+        <v>0</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0</v>
+      </c>
+      <c r="D15" s="11">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="I15" s="13">
-        <v>0</v>
-      </c>
-      <c r="J15" s="13" t="s">
+      <c r="I15" s="11">
+        <v>0</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="K15" s="13">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13">
-        <v>0</v>
-      </c>
-      <c r="N15" s="13" t="s">
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11">
+        <v>0</v>
+      </c>
+      <c r="N15" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="14"/>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="25"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="16">
-        <v>0</v>
-      </c>
-      <c r="C16" s="16">
-        <v>0</v>
-      </c>
-      <c r="D16" s="16">
-        <v>0</v>
-      </c>
-      <c r="E16" s="16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="16" t="s">
+      <c r="B16" s="13">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="I16" s="16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="16" t="s">
+      <c r="I16" s="13">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="K16" s="16">
-        <v>0</v>
-      </c>
-      <c r="L16" s="16">
-        <v>0</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0</v>
-      </c>
-      <c r="N16" s="16" t="s">
+      <c r="K16" s="13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="17"/>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="26"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B17" s="16">
-        <v>0</v>
-      </c>
-      <c r="C17" s="16">
-        <v>0</v>
-      </c>
-      <c r="D17" s="16">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
-        <v>0</v>
-      </c>
-      <c r="G17" s="16">
-        <v>0</v>
-      </c>
-      <c r="H17" s="16">
+      <c r="B17" s="13">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13">
+        <v>0</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
         <v>360</v>
       </c>
-      <c r="I17" s="16">
-        <v>0</v>
-      </c>
-      <c r="J17" s="16">
-        <v>0</v>
-      </c>
-      <c r="K17" s="16">
-        <v>0</v>
-      </c>
-      <c r="L17" s="16">
-        <v>0</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0</v>
-      </c>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="17"/>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="I17" s="13">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13">
+        <v>0</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="26"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="N18" s="10" t="s">
+      <c r="N18" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="O18" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="P18" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="Q18" s="10" t="s">
+      <c r="Q18" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="R18" s="10" t="s">
+      <c r="R18" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="S18" s="9" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="T18" s="24" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="L19" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="M19" s="13" t="s">
+      <c r="M19" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="N19" s="13" t="s">
+      <c r="N19" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="O19" s="13" t="s">
+      <c r="O19" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="P19" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="Q19" s="13" t="s">
+      <c r="Q19" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="R19" s="13" t="s">
+      <c r="R19" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="S19" s="14" t="s">
+      <c r="S19" s="11" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="T19" s="25" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="M20" s="13" t="s">
+      <c r="M20" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="N20" s="13" t="s">
+      <c r="N20" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="O20" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="P20" s="13" t="s">
+      <c r="P20" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="Q20" s="13" t="s">
+      <c r="Q20" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="R20" s="13"/>
-      <c r="S20" s="14" t="s">
+      <c r="R20" s="11"/>
+      <c r="S20" s="11" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="T20" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="13">
         <v>-188.1</v>
       </c>
-      <c r="C21" s="16">
-        <v>0</v>
-      </c>
-      <c r="D21" s="16">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16">
-        <v>0</v>
-      </c>
-      <c r="G21" s="16">
-        <v>0</v>
-      </c>
-      <c r="H21" s="16">
-        <v>0</v>
-      </c>
-      <c r="I21" s="16">
-        <v>0</v>
-      </c>
-      <c r="J21" s="16">
-        <v>0</v>
-      </c>
-      <c r="K21" s="16">
-        <v>0</v>
-      </c>
-      <c r="L21" s="16">
-        <v>0</v>
-      </c>
-      <c r="M21" s="16">
-        <v>0</v>
-      </c>
-      <c r="N21" s="16">
+      <c r="C21" s="13">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13">
+        <v>0</v>
+      </c>
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0</v>
+      </c>
+      <c r="N21" s="13">
         <v>-193.5</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O21" s="13">
         <v>-199</v>
       </c>
-      <c r="P21" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="17"/>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="P21" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="26"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="I22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K22" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="L22" s="16" t="s">
+      <c r="L22" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="N22" s="16" t="s">
+      <c r="N22" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="O22" s="16" t="s">
+      <c r="O22" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="P22" s="16" t="s">
+      <c r="P22" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="Q22" s="16" t="s">
+      <c r="Q22" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="R22" s="16"/>
-      <c r="S22" s="17" t="s">
+      <c r="R22" s="13"/>
+      <c r="S22" s="13" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="T22" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="13">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="11">
+        <v>0</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="D23" s="13">
-        <v>0</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-      <c r="G23" s="13">
+      <c r="D23" s="11">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11">
         <v>-616.13</v>
       </c>
-      <c r="H23" s="13">
-        <v>0</v>
-      </c>
-      <c r="I23" s="13">
+      <c r="H23" s="11">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
         <v>-616.14</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="11">
         <v>-616.14</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="K23" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="L23" s="13" t="s">
+      <c r="L23" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="M23" s="13" t="s">
+      <c r="M23" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="N23" s="13" t="s">
+      <c r="N23" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="14" t="s">
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="T23" s="25">
+        <v>-944.58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="17">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13">
         <v>-62.75</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="T24" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B25" s="16">
-        <v>0</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="B25" s="13">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="D25" s="16">
-        <v>0</v>
-      </c>
-      <c r="E25" s="16">
-        <v>0</v>
-      </c>
-      <c r="F25" s="16">
-        <v>0</v>
-      </c>
-      <c r="G25" s="16">
+      <c r="D25" s="13">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13">
         <v>-616.13</v>
       </c>
-      <c r="H25" s="16">
-        <v>0</v>
-      </c>
-      <c r="I25" s="16">
+      <c r="H25" s="13">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13">
         <v>-616.14</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="13">
         <v>-616.14</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K25" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="L25" s="16" t="s">
+      <c r="L25" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="M25" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="N25" s="16" t="s">
+      <c r="N25" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="17">
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13">
         <v>-944.58</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="T25" s="26">
+        <v>-944.58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="K26" s="13" t="s">
+      <c r="K26" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="L26" s="13" t="s">
+      <c r="L26" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="M26" s="13" t="s">
+      <c r="M26" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="N26" s="13" t="s">
+      <c r="N26" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="O26" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="P26" s="13" t="s">
+      <c r="P26" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="Q26" s="13" t="s">
+      <c r="Q26" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="R26" s="13" t="s">
+      <c r="R26" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="S26" s="14" t="s">
+      <c r="S26" s="11" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="T26" s="25" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="16">
-        <v>0</v>
-      </c>
-      <c r="C27" s="16">
-        <v>0</v>
-      </c>
-      <c r="D27" s="16">
-        <v>0</v>
-      </c>
-      <c r="E27" s="16">
-        <v>0</v>
-      </c>
-      <c r="F27" s="16">
-        <v>0</v>
-      </c>
-      <c r="G27" s="16">
-        <v>0</v>
-      </c>
-      <c r="H27" s="16">
-        <v>0</v>
-      </c>
-      <c r="I27" s="16">
-        <v>0</v>
-      </c>
-      <c r="J27" s="16">
-        <v>0</v>
-      </c>
-      <c r="K27" s="16">
-        <v>0</v>
-      </c>
-      <c r="L27" s="16" t="s">
+      <c r="B27" s="13">
+        <v>0</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M27" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16">
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13">
         <v>-120</v>
       </c>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="17"/>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="26"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B28" s="16">
-        <v>0</v>
-      </c>
-      <c r="C28" s="16">
-        <v>0</v>
-      </c>
-      <c r="D28" s="16">
+      <c r="B28" s="13">
+        <v>0</v>
+      </c>
+      <c r="C28" s="13">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
         <v>-120</v>
       </c>
-      <c r="E28" s="16">
-        <v>0</v>
-      </c>
-      <c r="F28" s="16">
-        <v>0</v>
-      </c>
-      <c r="G28" s="16">
-        <v>0</v>
-      </c>
-      <c r="H28" s="16">
-        <v>0</v>
-      </c>
-      <c r="I28" s="16">
-        <v>0</v>
-      </c>
-      <c r="J28" s="16">
-        <v>0</v>
-      </c>
-      <c r="K28" s="16">
-        <v>0</v>
-      </c>
-      <c r="L28" s="16">
-        <v>0</v>
-      </c>
-      <c r="M28" s="16">
-        <v>0</v>
-      </c>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="19"/>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="E28" s="13">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="27"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="13">
         <v>-516.66</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="13">
         <v>-412.64</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="13">
         <v>-618.96</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="13">
         <v>-618.96</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="13">
         <v>-428.73</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="13">
         <v>-428.73</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="Q29" s="13">
         <v>-428.73</v>
       </c>
-      <c r="R29" s="16">
+      <c r="R29" s="13">
         <v>-820.17</v>
       </c>
-      <c r="S29" s="17">
+      <c r="S29" s="13">
         <v>-475.35</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="T29" s="26">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="I30" s="16" t="s">
+      <c r="I30" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="J30" s="16" t="s">
+      <c r="J30" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="K30" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="L30" s="16" t="s">
+      <c r="L30" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="M30" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="N30" s="16" t="s">
+      <c r="N30" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="O30" s="16" t="s">
+      <c r="O30" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="P30" s="16" t="s">
+      <c r="P30" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="Q30" s="16" t="s">
+      <c r="Q30" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="R30" s="16" t="s">
+      <c r="R30" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="S30" s="17" t="s">
+      <c r="S30" s="13" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="T30" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16" t="s">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="S31" s="17"/>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="S31" s="13"/>
+      <c r="T31" s="26"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="J32" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="K32" s="16" t="s">
+      <c r="K32" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="16" t="s">
+      <c r="L32" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="M32" s="16" t="s">
+      <c r="M32" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="N32" s="16" t="s">
+      <c r="N32" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="O32" s="16" t="s">
+      <c r="O32" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="P32" s="16" t="s">
+      <c r="P32" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="Q32" s="16" t="s">
+      <c r="Q32" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="R32" s="16" t="s">
+      <c r="R32" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="S32" s="17" t="s">
+      <c r="S32" s="13" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="T32" s="26" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="13">
         <v>-52.76</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="13">
         <v>-52.76</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="13">
         <v>-52.76</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="13">
         <v>-52.76</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="13">
         <v>-52.76</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="O33" s="16">
+      <c r="O33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="P33" s="16">
+      <c r="P33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="Q33" s="16">
+      <c r="Q33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="R33" s="16">
+      <c r="R33" s="13">
         <v>-56.24</v>
       </c>
-      <c r="S33" s="17">
+      <c r="S33" s="13">
         <v>-59.28</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="T33" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="B34" s="16">
-        <v>0</v>
-      </c>
-      <c r="C34" s="16">
-        <v>0</v>
-      </c>
-      <c r="D34" s="16">
-        <v>0</v>
-      </c>
-      <c r="E34" s="16">
-        <v>0</v>
-      </c>
-      <c r="F34" s="16">
-        <v>0</v>
-      </c>
-      <c r="G34" s="16">
-        <v>0</v>
-      </c>
-      <c r="H34" s="16">
-        <v>0</v>
-      </c>
-      <c r="I34" s="16">
-        <v>0</v>
-      </c>
-      <c r="J34" s="16">
+      <c r="B34" s="13">
+        <v>0</v>
+      </c>
+      <c r="C34" s="13">
+        <v>0</v>
+      </c>
+      <c r="D34" s="13">
+        <v>0</v>
+      </c>
+      <c r="E34" s="13">
+        <v>0</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13">
         <v>-587</v>
       </c>
-      <c r="K34" s="16">
-        <v>0</v>
-      </c>
-      <c r="L34" s="16">
-        <v>0</v>
-      </c>
-      <c r="M34" s="16">
-        <v>0</v>
-      </c>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="19"/>
-    </row>
-    <row r="35" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="K34" s="13">
+        <v>0</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13">
+        <v>0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="27"/>
+    </row>
+    <row r="35" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="K35" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="L35" s="13" t="s">
+      <c r="L35" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="M35" s="13" t="s">
+      <c r="M35" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="N35" s="13" t="s">
+      <c r="N35" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="O35" s="13" t="s">
+      <c r="O35" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="P35" s="13" t="s">
+      <c r="P35" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="Q35" s="13" t="s">
+      <c r="Q35" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="R35" s="13" t="s">
+      <c r="R35" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="S35" s="14" t="s">
+      <c r="S35" s="11" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
+      <c r="T35" s="25" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B36" s="13">
-        <v>0</v>
-      </c>
-      <c r="C36" s="13">
-        <v>0</v>
-      </c>
-      <c r="D36" s="13">
-        <v>0</v>
-      </c>
-      <c r="E36" s="13">
-        <v>0</v>
-      </c>
-      <c r="F36" s="13">
-        <v>0</v>
-      </c>
-      <c r="G36" s="13">
-        <v>0</v>
-      </c>
-      <c r="H36" s="13">
+      <c r="B36" s="11">
+        <v>0</v>
+      </c>
+      <c r="C36" s="11">
+        <v>0</v>
+      </c>
+      <c r="D36" s="11">
+        <v>0</v>
+      </c>
+      <c r="E36" s="11">
+        <v>0</v>
+      </c>
+      <c r="F36" s="11">
+        <v>0</v>
+      </c>
+      <c r="G36" s="11">
+        <v>0</v>
+      </c>
+      <c r="H36" s="11">
         <v>-360</v>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="11">
         <v>-280.61</v>
       </c>
-      <c r="J36" s="13">
-        <v>0</v>
-      </c>
-      <c r="K36" s="13" t="s">
+      <c r="J36" s="11">
+        <v>0</v>
+      </c>
+      <c r="K36" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="L36" s="13">
-        <v>0</v>
-      </c>
-      <c r="M36" s="13" t="s">
+      <c r="L36" s="11">
+        <v>0</v>
+      </c>
+      <c r="M36" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="N36" s="13">
+      <c r="N36" s="11">
         <v>-293.74</v>
       </c>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13" t="s">
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="R36" s="13" t="s">
+      <c r="R36" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="S36" s="14">
+      <c r="S36" s="11">
         <v>-162.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+      <c r="T36" s="25"/>
+    </row>
+    <row r="37" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="B37" s="16">
-        <v>0</v>
-      </c>
-      <c r="C37" s="16">
-        <v>0</v>
-      </c>
-      <c r="D37" s="16">
-        <v>0</v>
-      </c>
-      <c r="E37" s="16">
-        <v>0</v>
-      </c>
-      <c r="F37" s="16">
-        <v>0</v>
-      </c>
-      <c r="G37" s="16">
-        <v>0</v>
-      </c>
-      <c r="H37" s="16">
-        <v>0</v>
-      </c>
-      <c r="I37" s="16">
+      <c r="B37" s="13">
+        <v>0</v>
+      </c>
+      <c r="C37" s="13">
+        <v>0</v>
+      </c>
+      <c r="D37" s="13">
+        <v>0</v>
+      </c>
+      <c r="E37" s="13">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13">
+        <v>0</v>
+      </c>
+      <c r="G37" s="13">
+        <v>0</v>
+      </c>
+      <c r="H37" s="13">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13">
         <v>-280.61</v>
       </c>
-      <c r="J37" s="16">
-        <v>0</v>
-      </c>
-      <c r="K37" s="16" t="s">
+      <c r="J37" s="13">
+        <v>0</v>
+      </c>
+      <c r="K37" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="L37" s="16">
-        <v>0</v>
-      </c>
-      <c r="M37" s="16" t="s">
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="13">
         <v>-293.74</v>
       </c>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="16" t="s">
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="R37" s="16" t="s">
+      <c r="R37" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="S37" s="17"/>
-      <c r="X37" s="22"/>
-    </row>
-    <row r="38" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="S37" s="13"/>
+      <c r="T37" s="26"/>
+      <c r="Y37" s="16"/>
+    </row>
+    <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="17">
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13">
         <v>-162.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="T38" s="26"/>
+    </row>
+    <row r="39" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="B39" s="16">
-        <v>0</v>
-      </c>
-      <c r="C39" s="16">
-        <v>0</v>
-      </c>
-      <c r="D39" s="16">
-        <v>0</v>
-      </c>
-      <c r="E39" s="16">
-        <v>0</v>
-      </c>
-      <c r="F39" s="16">
-        <v>0</v>
-      </c>
-      <c r="G39" s="16">
-        <v>0</v>
-      </c>
-      <c r="H39" s="16">
+      <c r="B39" s="13">
+        <v>0</v>
+      </c>
+      <c r="C39" s="13">
+        <v>0</v>
+      </c>
+      <c r="D39" s="13">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13">
+        <v>0</v>
+      </c>
+      <c r="G39" s="13">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13">
         <v>-360</v>
       </c>
-      <c r="I39" s="16">
-        <v>0</v>
-      </c>
-      <c r="J39" s="16">
-        <v>0</v>
-      </c>
-      <c r="K39" s="16">
-        <v>0</v>
-      </c>
-      <c r="L39" s="16">
-        <v>0</v>
-      </c>
-      <c r="M39" s="16">
-        <v>0</v>
-      </c>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="17"/>
-    </row>
-    <row r="40" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="I39" s="13">
+        <v>0</v>
+      </c>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
+      <c r="K39" s="13">
+        <v>0</v>
+      </c>
+      <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="13">
+        <v>0</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="26"/>
+    </row>
+    <row r="40" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="I40" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K40" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="L40" s="13" t="s">
+      <c r="L40" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="M40" s="13" t="s">
+      <c r="M40" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="N40" s="13" t="s">
+      <c r="N40" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="O40" s="13" t="s">
+      <c r="O40" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="P40" s="13" t="s">
+      <c r="P40" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="Q40" s="13" t="s">
+      <c r="Q40" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="R40" s="13" t="s">
+      <c r="R40" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="S40" s="14" t="s">
+      <c r="S40" s="11" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="T40" s="25" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="13">
         <v>-954.6</v>
       </c>
-      <c r="C41" s="16">
-        <v>0</v>
-      </c>
-      <c r="D41" s="16" t="s">
+      <c r="C41" s="13">
+        <v>0</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="I41" s="16" t="s">
+      <c r="I41" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="J41" s="16" t="s">
+      <c r="J41" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="K41" s="16" t="s">
+      <c r="K41" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="L41" s="16" t="s">
+      <c r="L41" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="M41" s="16" t="s">
+      <c r="M41" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16" t="s">
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="P41" s="16" t="s">
+      <c r="P41" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="Q41" s="16">
+      <c r="Q41" s="13">
         <v>-667.44</v>
       </c>
-      <c r="R41" s="16" t="s">
+      <c r="R41" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="S41" s="17" t="s">
+      <c r="S41" s="13" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="T41" s="26" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="G42" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="I42" s="16" t="s">
+      <c r="I42" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="J42" s="16" t="s">
+      <c r="J42" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="K42" s="16" t="s">
+      <c r="K42" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="L42" s="16" t="s">
+      <c r="L42" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="M42" s="16" t="s">
+      <c r="M42" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="N42" s="16" t="s">
+      <c r="N42" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="O42" s="16" t="s">
+      <c r="O42" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="P42" s="16" t="s">
+      <c r="P42" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="Q42" s="16" t="s">
+      <c r="Q42" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="R42" s="16" t="s">
+      <c r="R42" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="S42" s="17" t="s">
+      <c r="S42" s="13" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="T42" s="26" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="D43" s="16">
-        <v>0</v>
-      </c>
-      <c r="E43" s="16" t="s">
+      <c r="D43" s="13">
+        <v>0</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="16">
-        <v>0</v>
-      </c>
-      <c r="H43" s="16" t="s">
+      <c r="G43" s="13">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="I43" s="16" t="s">
+      <c r="I43" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="J43" s="16" t="s">
+      <c r="J43" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="K43" s="16" t="s">
+      <c r="K43" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="13">
         <v>-777.21</v>
       </c>
-      <c r="M43" s="16" t="s">
+      <c r="M43" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="N43" s="16">
+      <c r="N43" s="13">
         <v>-662.44</v>
       </c>
-      <c r="O43" s="16" t="s">
+      <c r="O43" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="P43" s="16" t="s">
+      <c r="P43" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="Q43" s="16" t="s">
+      <c r="Q43" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="R43" s="16" t="s">
+      <c r="R43" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="S43" s="17" t="s">
+      <c r="S43" s="13" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="T43" s="26" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="13">
         <v>-900</v>
       </c>
-      <c r="C44" s="16">
-        <v>0</v>
-      </c>
-      <c r="D44" s="16">
+      <c r="C44" s="13">
+        <v>0</v>
+      </c>
+      <c r="D44" s="13">
         <v>-700</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="13">
         <v>-300</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="G44" s="16">
-        <v>0</v>
-      </c>
-      <c r="H44" s="16">
+      <c r="G44" s="13">
+        <v>0</v>
+      </c>
+      <c r="H44" s="13">
         <v>-650</v>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="13">
         <v>-700</v>
       </c>
-      <c r="J44" s="16" t="s">
+      <c r="J44" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="13">
         <v>-350</v>
       </c>
-      <c r="L44" s="16">
+      <c r="L44" s="13">
         <v>-350</v>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="13">
         <v>-200</v>
       </c>
-      <c r="N44" s="16">
+      <c r="N44" s="13">
         <v>-500</v>
       </c>
-      <c r="O44" s="16">
+      <c r="O44" s="13">
         <v>-500</v>
       </c>
-      <c r="P44" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="16">
+      <c r="P44" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="13">
         <v>-250</v>
       </c>
-      <c r="R44" s="16" t="s">
+      <c r="R44" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="S44" s="17" t="s">
+      <c r="S44" s="13" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="T44" s="26" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="C45" s="16">
-        <v>0</v>
-      </c>
-      <c r="D45" s="16">
+      <c r="C45" s="13">
+        <v>0</v>
+      </c>
+      <c r="D45" s="13">
         <v>-938.8</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="F45" s="16" t="s">
+      <c r="F45" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="I45" s="16" t="s">
+      <c r="I45" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="J45" s="16" t="s">
+      <c r="J45" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="K45" s="16" t="s">
+      <c r="K45" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="L45" s="16" t="s">
+      <c r="L45" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="M45" s="16" t="s">
+      <c r="M45" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="N45" s="16" t="s">
+      <c r="N45" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="O45" s="16" t="s">
+      <c r="O45" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="P45" s="16" t="s">
+      <c r="P45" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="Q45" s="16" t="s">
+      <c r="Q45" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="R45" s="16" t="s">
+      <c r="R45" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="S45" s="17" t="s">
+      <c r="S45" s="13" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+      <c r="T45" s="26" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="13">
         <v>-380</v>
       </c>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="H46" s="16" t="s">
+      <c r="H46" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="I46" s="16" t="s">
+      <c r="I46" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="J46" s="16">
-        <v>0</v>
-      </c>
-      <c r="K46" s="16" t="s">
+      <c r="J46" s="13">
+        <v>0</v>
+      </c>
+      <c r="K46" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="L46" s="16" t="s">
+      <c r="L46" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="M46" s="16" t="s">
+      <c r="M46" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="N46" s="16">
+      <c r="N46" s="13">
         <v>-380</v>
       </c>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16" t="s">
+      <c r="O46" s="13"/>
+      <c r="P46" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16" t="s">
+      <c r="Q46" s="13"/>
+      <c r="R46" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="S46" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+      <c r="S46" s="13">
+        <v>0</v>
+      </c>
+      <c r="T46" s="26" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="13">
         <v>-549.21</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="G47" s="16" t="s">
+      <c r="G47" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H47" s="16">
+      <c r="H47" s="13">
         <v>-689.25</v>
       </c>
-      <c r="I47" s="16" t="s">
+      <c r="I47" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="J47" s="16" t="s">
+      <c r="J47" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="K47" s="16" t="s">
+      <c r="K47" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="L47" s="16" t="s">
+      <c r="L47" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="M47" s="16">
+      <c r="M47" s="13">
         <v>-748.59</v>
       </c>
-      <c r="N47" s="16">
+      <c r="N47" s="13">
         <v>-671.08</v>
       </c>
-      <c r="O47" s="16" t="s">
+      <c r="O47" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="P47" s="16">
+      <c r="P47" s="13">
         <v>-930.55</v>
       </c>
-      <c r="Q47" s="16" t="s">
+      <c r="Q47" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="R47" s="16">
+      <c r="R47" s="13">
         <v>-921.31</v>
       </c>
-      <c r="S47" s="17" t="s">
+      <c r="S47" s="13" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
+      <c r="T47" s="26" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="F48" s="13">
-        <v>0</v>
-      </c>
-      <c r="G48" s="13">
-        <v>0</v>
-      </c>
-      <c r="H48" s="13" t="s">
+      <c r="F48" s="11">
+        <v>0</v>
+      </c>
+      <c r="G48" s="11">
+        <v>0</v>
+      </c>
+      <c r="H48" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="I48" s="13">
-        <v>0</v>
-      </c>
-      <c r="J48" s="13" t="s">
+      <c r="I48" s="11">
+        <v>0</v>
+      </c>
+      <c r="J48" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="K48" s="13" t="s">
+      <c r="K48" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="L48" s="13">
+      <c r="L48" s="11">
         <v>-270</v>
       </c>
-      <c r="M48" s="13">
+      <c r="M48" s="11">
         <v>-270</v>
       </c>
-      <c r="N48" s="13" t="s">
+      <c r="N48" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="O48" s="23"/>
-      <c r="P48" s="13" t="s">
+      <c r="O48" s="17"/>
+      <c r="P48" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="Q48" s="13" t="s">
+      <c r="Q48" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="R48" s="13" t="s">
+      <c r="R48" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="S48" s="14" t="s">
+      <c r="S48" s="11" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+      <c r="T48" s="25" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="E49" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="F49" s="16">
-        <v>0</v>
-      </c>
-      <c r="G49" s="16">
-        <v>0</v>
-      </c>
-      <c r="H49" s="16" t="s">
+      <c r="F49" s="13">
+        <v>0</v>
+      </c>
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="I49" s="16">
-        <v>0</v>
-      </c>
-      <c r="J49" s="16" t="s">
+      <c r="I49" s="13">
+        <v>0</v>
+      </c>
+      <c r="J49" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="K49" s="16" t="s">
+      <c r="K49" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="13">
         <v>-270</v>
       </c>
-      <c r="M49" s="16">
+      <c r="M49" s="13">
         <v>-270</v>
       </c>
-      <c r="N49" s="16" t="s">
+      <c r="N49" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="O49" s="18"/>
-      <c r="P49" s="16" t="s">
+      <c r="O49" s="14"/>
+      <c r="P49" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="Q49" s="16" t="s">
+      <c r="Q49" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="R49" s="16" t="s">
+      <c r="R49" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="S49" s="17" t="s">
+      <c r="S49" s="13" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
+      <c r="T49" s="26" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="B50" s="13">
-        <v>0</v>
-      </c>
-      <c r="C50" s="13">
-        <v>0</v>
-      </c>
-      <c r="D50" s="13">
-        <v>0</v>
-      </c>
-      <c r="E50" s="13">
-        <v>0</v>
-      </c>
-      <c r="F50" s="13">
-        <v>0</v>
-      </c>
-      <c r="G50" s="13">
-        <v>0</v>
-      </c>
-      <c r="H50" s="13">
-        <v>0</v>
-      </c>
-      <c r="I50" s="13">
-        <v>0</v>
-      </c>
-      <c r="J50" s="13">
+      <c r="B50" s="11">
+        <v>0</v>
+      </c>
+      <c r="C50" s="11">
+        <v>0</v>
+      </c>
+      <c r="D50" s="11">
+        <v>0</v>
+      </c>
+      <c r="E50" s="11">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11">
+        <v>0</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11">
+        <v>0</v>
+      </c>
+      <c r="J50" s="11">
         <v>-4</v>
       </c>
-      <c r="K50" s="13">
-        <v>0</v>
-      </c>
-      <c r="L50" s="13">
-        <v>0</v>
-      </c>
-      <c r="M50" s="13">
-        <v>0</v>
-      </c>
-      <c r="N50" s="13">
+      <c r="K50" s="11">
+        <v>0</v>
+      </c>
+      <c r="L50" s="11">
+        <v>0</v>
+      </c>
+      <c r="M50" s="11">
+        <v>0</v>
+      </c>
+      <c r="N50" s="11">
         <v>-4</v>
       </c>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
-      <c r="S50" s="24"/>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="15" t="s">
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="29"/>
+    </row>
+    <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="B51" s="16">
-        <v>0</v>
-      </c>
-      <c r="C51" s="16">
-        <v>0</v>
-      </c>
-      <c r="D51" s="16">
-        <v>0</v>
-      </c>
-      <c r="E51" s="16">
-        <v>0</v>
-      </c>
-      <c r="F51" s="16">
-        <v>0</v>
-      </c>
-      <c r="G51" s="16">
-        <v>0</v>
-      </c>
-      <c r="H51" s="16">
-        <v>0</v>
-      </c>
-      <c r="I51" s="16">
-        <v>0</v>
-      </c>
-      <c r="J51" s="16">
+      <c r="B51" s="13">
+        <v>0</v>
+      </c>
+      <c r="C51" s="13">
+        <v>0</v>
+      </c>
+      <c r="D51" s="13">
+        <v>0</v>
+      </c>
+      <c r="E51" s="13">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13">
+        <v>0</v>
+      </c>
+      <c r="G51" s="13">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
+        <v>0</v>
+      </c>
+      <c r="I51" s="13">
+        <v>0</v>
+      </c>
+      <c r="J51" s="13">
         <v>-4</v>
       </c>
-      <c r="K51" s="16">
-        <v>0</v>
-      </c>
-      <c r="L51" s="16">
-        <v>0</v>
-      </c>
-      <c r="M51" s="16">
-        <v>0</v>
-      </c>
-      <c r="N51" s="16">
+      <c r="K51" s="13">
+        <v>0</v>
+      </c>
+      <c r="L51" s="13">
+        <v>0</v>
+      </c>
+      <c r="M51" s="13">
+        <v>0</v>
+      </c>
+      <c r="N51" s="13">
         <v>-4</v>
       </c>
-      <c r="O51" s="18"/>
-      <c r="P51" s="18"/>
-      <c r="Q51" s="18"/>
-      <c r="R51" s="18"/>
-      <c r="S51" s="19"/>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
+      <c r="O51" s="14"/>
+      <c r="P51" s="14"/>
+      <c r="Q51" s="14"/>
+      <c r="R51" s="14"/>
+      <c r="S51" s="14"/>
+      <c r="T51" s="27"/>
+    </row>
+    <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="11">
         <v>-174.07</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="D52" s="13">
-        <v>0</v>
-      </c>
-      <c r="E52" s="13">
-        <v>0</v>
-      </c>
-      <c r="F52" s="13">
-        <v>0</v>
-      </c>
-      <c r="G52" s="13">
-        <v>0</v>
-      </c>
-      <c r="H52" s="13">
-        <v>0</v>
-      </c>
-      <c r="I52" s="13">
-        <v>0</v>
-      </c>
-      <c r="J52" s="13">
-        <v>0</v>
-      </c>
-      <c r="K52" s="13">
-        <v>0</v>
-      </c>
-      <c r="L52" s="13" t="s">
+      <c r="D52" s="11">
+        <v>0</v>
+      </c>
+      <c r="E52" s="11">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11">
+        <v>0</v>
+      </c>
+      <c r="G52" s="11">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11">
+        <v>0</v>
+      </c>
+      <c r="J52" s="11">
+        <v>0</v>
+      </c>
+      <c r="K52" s="11">
+        <v>0</v>
+      </c>
+      <c r="L52" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="M52" s="13">
+      <c r="M52" s="11">
         <v>-32.380000000000003</v>
       </c>
-      <c r="N52" s="13"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="13" t="s">
+      <c r="N52" s="11"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="R52" s="13"/>
-      <c r="S52" s="14"/>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+      <c r="T52" s="25"/>
+    </row>
+    <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="13">
         <v>-174.07</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="D53" s="16">
-        <v>0</v>
-      </c>
-      <c r="E53" s="16">
-        <v>0</v>
-      </c>
-      <c r="F53" s="16">
-        <v>0</v>
-      </c>
-      <c r="G53" s="16">
-        <v>0</v>
-      </c>
-      <c r="H53" s="16">
-        <v>0</v>
-      </c>
-      <c r="I53" s="16">
-        <v>0</v>
-      </c>
-      <c r="J53" s="16">
-        <v>0</v>
-      </c>
-      <c r="K53" s="16">
-        <v>0</v>
-      </c>
-      <c r="L53" s="16" t="s">
+      <c r="D53" s="13">
+        <v>0</v>
+      </c>
+      <c r="E53" s="13">
+        <v>0</v>
+      </c>
+      <c r="F53" s="13">
+        <v>0</v>
+      </c>
+      <c r="G53" s="13">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="13">
+        <v>0</v>
+      </c>
+      <c r="K53" s="13">
+        <v>0</v>
+      </c>
+      <c r="L53" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="M53" s="16">
+      <c r="M53" s="13">
         <v>-32.380000000000003</v>
       </c>
-      <c r="N53" s="16"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="16" t="s">
+      <c r="N53" s="13"/>
+      <c r="O53" s="14"/>
+      <c r="P53" s="14"/>
+      <c r="Q53" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="R53" s="16"/>
-      <c r="S53" s="17"/>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="15" t="s">
+      <c r="R53" s="13"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="26"/>
+    </row>
+    <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="B54" s="16">
-        <v>0</v>
-      </c>
-      <c r="C54" s="16">
-        <v>0</v>
-      </c>
-      <c r="D54" s="16">
-        <v>0</v>
-      </c>
-      <c r="E54" s="16">
-        <v>0</v>
-      </c>
-      <c r="F54" s="16">
-        <v>0</v>
-      </c>
-      <c r="G54" s="16">
-        <v>0</v>
-      </c>
-      <c r="H54" s="16">
-        <v>0</v>
-      </c>
-      <c r="I54" s="16">
-        <v>0</v>
-      </c>
-      <c r="J54" s="16">
-        <v>0</v>
-      </c>
-      <c r="K54" s="16">
-        <v>0</v>
-      </c>
-      <c r="L54" s="16">
+      <c r="B54" s="13">
+        <v>0</v>
+      </c>
+      <c r="C54" s="13">
+        <v>0</v>
+      </c>
+      <c r="D54" s="13">
+        <v>0</v>
+      </c>
+      <c r="E54" s="13">
+        <v>0</v>
+      </c>
+      <c r="F54" s="13">
+        <v>0</v>
+      </c>
+      <c r="G54" s="13">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0</v>
+      </c>
+      <c r="J54" s="13">
+        <v>0</v>
+      </c>
+      <c r="K54" s="13">
+        <v>0</v>
+      </c>
+      <c r="L54" s="13">
         <v>-18.079999999999998</v>
       </c>
-      <c r="M54" s="16">
-        <v>0</v>
-      </c>
-      <c r="N54" s="16"/>
-      <c r="O54" s="18"/>
-      <c r="P54" s="18"/>
-      <c r="Q54" s="18"/>
-      <c r="R54" s="18"/>
-      <c r="S54" s="19"/>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M54" s="13">
+        <v>0</v>
+      </c>
+      <c r="N54" s="13"/>
+      <c r="O54" s="14"/>
+      <c r="P54" s="14"/>
+      <c r="Q54" s="14"/>
+      <c r="R54" s="14"/>
+      <c r="S54" s="14"/>
+      <c r="T54" s="27"/>
+    </row>
+    <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I55" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="J55" s="10" t="s">
+      <c r="J55" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="L55" s="10" t="s">
+      <c r="L55" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="M55" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="N55" s="10" t="s">
+      <c r="N55" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="O55" s="25" t="s">
+      <c r="O55" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="P55" s="26" t="s">
+      <c r="P55" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="Q55" s="26" t="s">
+      <c r="Q55" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="R55" s="26" t="s">
+      <c r="R55" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="S55" s="27" t="s">
+      <c r="S55" s="19" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="28" t="s">
+      <c r="T55" s="30" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B56" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="21" t="s">
         <v>421</v>
       </c>
-      <c r="D56" s="29" t="s">
+      <c r="D56" s="21" t="s">
         <v>422</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="21" t="s">
         <v>423</v>
       </c>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="21" t="s">
         <v>424</v>
       </c>
-      <c r="G56" s="29" t="s">
+      <c r="G56" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="H56" s="29" t="s">
+      <c r="H56" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="I56" s="29" t="s">
+      <c r="I56" s="21" t="s">
         <v>427</v>
       </c>
-      <c r="J56" s="29" t="s">
+      <c r="J56" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="K56" s="29" t="s">
+      <c r="K56" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="L56" s="29" t="s">
+      <c r="L56" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="M56" s="29" t="s">
+      <c r="M56" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="N56" s="29" t="s">
+      <c r="N56" s="21" t="s">
         <v>432</v>
       </c>
-      <c r="O56" s="29" t="s">
+      <c r="O56" s="21" t="s">
         <v>433</v>
       </c>
-      <c r="P56" s="29" t="s">
+      <c r="P56" s="21" t="s">
         <v>434</v>
       </c>
-      <c r="Q56" s="29" t="s">
+      <c r="Q56" s="21" t="s">
         <v>435</v>
       </c>
-      <c r="R56" s="29" t="s">
+      <c r="R56" s="21" t="s">
         <v>436</v>
       </c>
-      <c r="S56" s="30" t="s">
+      <c r="S56" s="21" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="31"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T56" s="31" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B63" s="22"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="B1:T1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:S3">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="greaterThan">
+  <conditionalFormatting sqref="A3:T3">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A18:S18">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
+  <conditionalFormatting sqref="A18:T18">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:O56">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M55:O55 C55 G55 K55">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55:O55">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O55 B55:N56">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="14" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O56:S56">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="O56:T56">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P56:S56">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="P56:T56">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q55">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
       <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S55">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="21.429,28">
-      <formula>NOT(ISERROR(SEARCH("21.429,28",S55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
